--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20212.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="104">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,258 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CITALAN</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>BONOLA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>GUILLEN</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>VELEZ</t>
+  </si>
+  <si>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>BUENO</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>MERINO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>TLEHUACTLE</t>
+  </si>
+  <si>
+    <t>VALERDE</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>JOSE ABRAHAM</t>
+  </si>
+  <si>
+    <t>JOSE MATEO</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>MARCOS URIEL</t>
+  </si>
+  <si>
+    <t>CRISTAL</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>IAN ISSAID</t>
+  </si>
+  <si>
+    <t>MICHELL</t>
+  </si>
+  <si>
+    <t>MICAELA</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>EDITH</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>ROSARIO DOLORES</t>
+  </si>
+  <si>
+    <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
+    <t>JORGE LUIS</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>LUIS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>JUDITH ESTEFANIA</t>
   </si>
 </sst>
 </file>
@@ -477,16 +729,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>40.63</v>
+      </c>
+      <c r="H2">
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -500,16 +755,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>60.61</v>
+      </c>
+      <c r="H3">
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -523,16 +781,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H4">
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -546,16 +807,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>81.81999999999999</v>
+      </c>
+      <c r="H5">
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -611,7 +875,7 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -634,7 +898,7 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -657,7 +921,7 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -680,7 +944,7 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -739,16 +1003,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>40.63</v>
+      </c>
+      <c r="H2">
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -762,16 +1029,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>60.61</v>
+      </c>
+      <c r="H3">
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -785,16 +1055,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H4">
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -808,16 +1081,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>81.81999999999999</v>
+      </c>
+      <c r="H5">
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -827,7 +1103,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -857,6 +1133,719 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920021</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920025</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920026</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920029</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920031</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920035</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920037</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920045</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920046</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920052</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920056</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920150</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920154</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>19330051920158</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>19330051920159</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>19330051920162</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>19330051920178</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>19330051920195</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>19330051920202</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>18330051920351</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" t="s">
+        <v>92</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920002</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920004</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920011</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" t="s">
+        <v>95</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920012</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>20330051920013</v>
+      </c>
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" t="s">
+        <v>97</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920015</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920060</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920027</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" t="s">
+        <v>100</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>19330051920200</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>19330051920206</v>
+      </c>
+      <c r="B31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" t="s">
+        <v>102</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>19330051920214</v>
+      </c>
+      <c r="B32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20212.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -79,256 +79,43 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
     <t>XOCUA</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CITALAN</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>BONOLA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
     <t>GUILLEN</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>VELEZ</t>
-  </si>
-  <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>BUENO</t>
-  </si>
-  <si>
     <t>ESPIRITU</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
     <t>SEGURA</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
     <t>LINARES</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
     <t>TEQUIHUATLE</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>TLEHUACTLE</t>
-  </si>
-  <si>
-    <t>VALERDE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>JOSE ABRAHAM</t>
-  </si>
-  <si>
-    <t>JOSE MATEO</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
     <t>MARCOS URIEL</t>
   </si>
   <si>
-    <t>CRISTAL</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
     <t>CESAR</t>
   </si>
   <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>IAN ISSAID</t>
-  </si>
-  <si>
-    <t>MICHELL</t>
-  </si>
-  <si>
-    <t>MICAELA</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
     <t>EDITH</t>
   </si>
   <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>ROSARIO DOLORES</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ALAIN</t>
-  </si>
-  <si>
-    <t>JORGE LUIS</t>
-  </si>
-  <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
     <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>LUIS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>JUDITH ESTEFANIA</t>
   </si>
 </sst>
 </file>
@@ -729,19 +516,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>40.63</v>
+        <v>87.5</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -755,19 +542,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>60.61</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -781,19 +568,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>71.43000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -807,19 +594,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>81.81999999999999</v>
+        <v>96.97</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +662,7 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -898,7 +685,7 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -921,7 +708,7 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -944,7 +731,7 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1003,19 +790,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>40.63</v>
+        <v>87.5</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1029,19 +816,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>60.61</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1055,19 +842,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>71.43000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1081,19 +868,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>81.81999999999999</v>
+        <v>96.97</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -1103,7 +890,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1135,16 +922,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920021</v>
+        <v>20330051920035</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1158,22 +945,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920025</v>
+        <v>20330051920052</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1181,22 +968,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920026</v>
+        <v>19330051920195</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1204,16 +991,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920029</v>
+        <v>20330051920011</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1222,21 +1009,21 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920031</v>
+        <v>20330051920012</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1245,604 +1032,6 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920035</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920037</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920045</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920046</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920052</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920056</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920150</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920154</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" t="s">
-        <v>85</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920158</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920159</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920162</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" t="s">
-        <v>88</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920178</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" t="s">
-        <v>89</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920195</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" t="s">
-        <v>90</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920202</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>91</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>18330051920351</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" t="s">
-        <v>92</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920002</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920004</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920011</v>
-      </c>
-      <c r="B24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" t="s">
-        <v>95</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920012</v>
-      </c>
-      <c r="B25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920013</v>
-      </c>
-      <c r="B26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" t="s">
-        <v>97</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920015</v>
-      </c>
-      <c r="B27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" t="s">
-        <v>68</v>
-      </c>
-      <c r="D27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920060</v>
-      </c>
-      <c r="B28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" t="s">
-        <v>99</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920027</v>
-      </c>
-      <c r="B29" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" t="s">
-        <v>100</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>19330051920200</v>
-      </c>
-      <c r="B30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" t="s">
-        <v>101</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>19330051920206</v>
-      </c>
-      <c r="B31" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" t="s">
-        <v>102</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>19330051920214</v>
-      </c>
-      <c r="B32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" t="s">
-        <v>103</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20212.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,45 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>MARCOS URIEL</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
   </si>
 </sst>
 </file>
@@ -565,22 +526,22 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>34</v>
       </c>
       <c r="G4">
-        <v>97.14</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -659,16 +620,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -682,16 +646,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>75.76000000000001</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -702,19 +669,22 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>85.29000000000001</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -728,16 +698,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>93.94</v>
+      </c>
+      <c r="H5">
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -793,16 +766,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>87.5</v>
+        <v>96.88</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -819,16 +792,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>81.81999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -839,22 +812,22 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>34</v>
       </c>
       <c r="G4">
-        <v>97.14</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -871,16 +844,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -890,7 +863,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -920,121 +893,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920035</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920052</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920195</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920011</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920012</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20212.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,30 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>JOSE ABRAHAM</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
+  </si>
+  <si>
+    <t>BENY ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -620,19 +644,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>84.38</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -646,7 +670,7 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>8</v>
@@ -658,7 +682,7 @@
         <v>75.76000000000001</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -672,19 +696,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>85.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -698,19 +722,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -766,16 +790,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>96.88</v>
+        <v>84.38</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -792,16 +816,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>84.84999999999999</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -827,7 +851,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -853,7 +877,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -863,7 +887,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -893,6 +917,72 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920026</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920099</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920109</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20212.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20212.xlsx
@@ -980,7 +980,7 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20212.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -82,25 +82,10 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
     <t>JOSE ABRAHAM</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
-  </si>
-  <si>
-    <t>BENY ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -790,16 +775,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>84.38</v>
+        <v>96.88</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -816,16 +801,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>75.76000000000001</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -851,7 +836,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -877,7 +862,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -887,7 +872,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -925,10 +910,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -937,50 +922,7 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920099</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920109</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20212.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -82,10 +82,19 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
     <t>JOSE ABRAHAM</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
   </si>
 </sst>
 </file>
@@ -872,7 +881,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -910,10 +919,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -922,6 +931,29 @@
         <v>10</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920097</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
     </row>
